--- a/backend/foundation_masters.xlsx
+++ b/backend/foundation_masters.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード" sheetId="1" r:id="R29c70fcb24904394"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="システム設定" sheetId="2" r:id="Re8a1065385254f15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面ヘルプ" sheetId="3" r:id="Re435b90ee1464733"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行形式" sheetId="4" r:id="R3af242ef2e7b4123"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行列" sheetId="5" r:id="R5ddbe24bd6f2462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控除規則" sheetId="6" r:id="R2ea2844e0c0640a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採番" sheetId="7" r:id="R3ead07de7a5b44e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード" sheetId="1" r:id="R709a0a0d4a364bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="システム設定" sheetId="2" r:id="R7a4154038edb46d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面ヘルプ" sheetId="3" r:id="Rc6e7f60038464452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行形式" sheetId="4" r:id="R14b713650c8c4b81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="銀行列" sheetId="5" r:id="R7b5495dc13be4e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控除規則" sheetId="6" r:id="R1bdd5685b88a49a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採番" sheetId="7" r:id="R1bb5c97c0e764721"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2717,6 +2717,76 @@
         <x:v>権限変更は対象利用者の次回画面表示から反映されます。</x:v>
       </x:c>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>db_import</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>DB取込のヘルプ</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>編集用Excelを検証して、正常行だけDBへ登録・更新します。</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>出力後に画面で変更されたレコードは競合として除外します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>db_export</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>DB出力のヘルプ</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>現行DBのマスター値を編集用Excelへ出力します。</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>修正したExcelはDB取込で検証します。Excelで消した行はDBから削除されません。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>master_data_export</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>マスターデータ出力のヘルプ</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>システムに同梱した基盤マスター初期値を取得します。</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>現行DBの値を確認する場合はDB出力を使用します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>test_data</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>検証用データのヘルプ</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>検証用データを設計・確認します。</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>作成は検証専用環境・DBでだけ可能です。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>menu_access_settings</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>利用可能メニュー選択のヘルプ</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>役割ごとに利用できるメニューを設定します。</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>承認・取消などの追加制限は変更しません。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
